--- a/result/平均クラスター係数基準/お互いにDP(dense_infl_p1_egotwitter).xlsx
+++ b/result/平均クラスター係数基準/お互いにDP(dense_infl_p1_egotwitter).xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -112,7 +112,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.000000%"/>
-    <numFmt numFmtId="181" formatCode="0.000%"/>
+    <numFmt numFmtId="177" formatCode="0.000%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -174,7 +174,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>

--- a/result/平均クラスター係数基準/お互いにDP(dense_infl_p1_egotwitter).xlsx
+++ b/result/平均クラスター係数基準/お互いにDP(dense_infl_p1_egotwitter).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaoriogawa/研究/community-detection-social-networks/result/平均クラスター係数基準/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587B1EA0-0D41-F642-87B6-9DF2000E190F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C58650B-4102-8E42-B1BF-D9AC0AA5B463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2640" yWindow="1500" windowWidth="28300" windowHeight="17360" xr2:uid="{C6F5C33C-B90F-B549-9C90-0D62FD2DC283}"/>
   </bookViews>
